--- a/fixErrorAllergyCode/ig/ValueSet-fr-vs-allergy-code.xlsx
+++ b/fixErrorAllergyCode/ig/ValueSet-fr-vs-allergy-code.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
-    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
-    <sheet name="Include ValueSet #4" r:id="rId8" sheetId="6"/>
+    <sheet name="Include ValueSet #3" r:id="rId7" sheetId="5"/>
+    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T13:38:14+00:00</t>
+    <t>2026-03-30T14:01:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,16 +123,16 @@
     <t>https://smt.esante.gouv.fr/terminologie-cip_ucd</t>
   </si>
   <si>
+    <t>http://id.who.int/icd/release/11/mms</t>
+  </si>
+  <si>
+    <t>ValueSet URL</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-allergie-vaccin-cisis</t>
+  </si>
+  <si>
     <t>https://smt.esante.gouv.fr/terminologie-sms</t>
-  </si>
-  <si>
-    <t>http://id.who.int/icd/release/11/mms</t>
-  </si>
-  <si>
-    <t>ValueSet URL</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-allergie-vaccin-cisis</t>
   </si>
 </sst>
 </file>
@@ -514,6 +514,30 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -544,30 +568,6 @@
         <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
         <v>36</v>
       </c>
     </row>
